--- a/KURIKULUM2026_REVISI/023_BUKU_KPT_SISTEKIN_2026_STRUKTUR_KPT2024.xlsx
+++ b/KURIKULUM2026_REVISI/023_BUKU_KPT_SISTEKIN_2026_STRUKTUR_KPT2024.xlsx
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C221" s="8" t="inlineStr">
         <is>
-          <t>Peminatan MK-2 &amp; MK-3 (6), `STI-624` Integrasi AI (3), `STI-627` Platform Eng (3), `STI-625` Smart City (2), `STI-626` Deep Learning (+P) (3), `FST-611` Metopel (2)</t>
+          <t>Peminatan MK-2 &amp; MK-3 (6), `STI-726` Integrasi AI (3), `STI-727` Platform Eng (3), `STI-727` Smart City (2), `STI-726` Deep Learning (+P) (3), `FST-611` Metopel (2)</t>
         </is>
       </c>
       <c r="D221" s="7" t="inlineStr">
